--- a/data/Output/result.xlsx
+++ b/data/Output/result.xlsx
@@ -68,7 +68,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -90,11 +90,55 @@
         <color rgb="00000000"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -109,6 +153,8 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -474,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A5:I14"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -488,20 +534,24 @@
     <col width="42" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
+    <row r="1"/>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
           <t>Week: 05/04/2026 - 05/08/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
-      <c r="G5" s="2" t="n"/>
-      <c r="H5" s="2" t="n"/>
-      <c r="I5" s="2" t="n"/>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="8" t="n"/>
+      <c r="F5" s="8" t="n"/>
+      <c r="G5" s="8" t="n"/>
+      <c r="H5" s="8" t="n"/>
+      <c r="I5" s="9" t="n"/>
     </row>
     <row r="6" ht="25" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
@@ -830,9 +880,698 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Week: 05/11/2026 - 05/15/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="n"/>
+      <c r="C18" s="8" t="n"/>
+      <c r="D18" s="8" t="n"/>
+      <c r="E18" s="8" t="n"/>
+      <c r="F18" s="8" t="n"/>
+      <c r="G18" s="8" t="n"/>
+      <c r="H18" s="8" t="n"/>
+      <c r="I18" s="9" t="n"/>
+    </row>
+    <row r="19" ht="25" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Productive Active Hrs</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Productive Passive Hrs</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Total Productive Hrs</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Active Days</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>GOAL</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Productive Hrs/Day</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>Comments</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Angie Carolina Guaman</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>7000 - INFORMATION TECHNOLOGY</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="H20" s="7" t="n">
+        <v>8.574999999999999</v>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Daniel Uribe</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>7000 - INFORMATION TECHNOLOGY</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>David Velasquez</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>7000 - INFORMATION TECHNOLOGY</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Juan David Londono</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>7000 - INFORMATION TECHNOLOGY</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="H23" s="7" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Juan Jose Gonzalez</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>7000 - INFORMATION TECHNOLOGY</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="H24" s="7" t="n">
+        <v>8.225</v>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>PTO 05/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Luis Aznar</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>7000 - INFORMATION TECHNOLOGY</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Paulina Parra</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>7000 - INFORMATION TECHNOLOGY</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D26" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E26" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F26" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="H26" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Sick leave</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Sheyla Salvatierra</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>7000 - INFORMATION TECHNOLOGY</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="D27" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="H27" s="7" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>PTO 05/07 y 05/08</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Week: 05/18/2026 - 05/22/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n"/>
+      <c r="E31" s="2" t="n"/>
+      <c r="F31" s="2" t="n"/>
+      <c r="G31" s="2" t="n"/>
+      <c r="H31" s="2" t="n"/>
+      <c r="I31" s="2" t="n"/>
+    </row>
+    <row r="32" ht="25" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Productive Active Hrs</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Productive Passive Hrs</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Total Productive Hrs</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Active Days</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>GOAL</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Productive Hrs/Day</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>Comments</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Angie Carolina Guaman</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>7000 - INFORMATION TECHNOLOGY</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="H33" s="7" t="n">
+        <v>8.574999999999999</v>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Daniel Uribe</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>7000 - INFORMATION TECHNOLOGY</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="D34" s="6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="H34" s="6" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>David Velasquez</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>7000 - INFORMATION TECHNOLOGY</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="H35" s="6" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Juan David Londono</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>7000 - INFORMATION TECHNOLOGY</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="D36" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="H36" s="7" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Juan Jose Gonzalez</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>7000 - INFORMATION TECHNOLOGY</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="D37" s="6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="H37" s="7" t="n">
+        <v>8.225</v>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>PTO 05/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Luis Aznar</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>7000 - INFORMATION TECHNOLOGY</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="D38" s="6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="H38" s="6" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Paulina Parra</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>7000 - INFORMATION TECHNOLOGY</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="D39" s="6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="H39" s="7" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Sick leave</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Sheyla Salvatierra</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>7000 - INFORMATION TECHNOLOGY</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="D40" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="H40" s="7" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>PTO 05/07 y 05/08</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="3">
     <mergeCell ref="A5:I5"/>
+    <mergeCell ref="A18:I18"/>
+    <mergeCell ref="A31:I31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Output/result.xlsx
+++ b/data/Output/result.xlsx
@@ -68,7 +68,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -90,55 +90,11 @@
         <color rgb="00000000"/>
       </bottom>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="00000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="00000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -153,8 +109,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -520,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A5:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -534,24 +488,20 @@
     <col width="42" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Week: 05/04/2026 - 05/08/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
-      <c r="H5" s="8" t="n"/>
-      <c r="I5" s="9" t="n"/>
+          <t>Week: 05/18/2026 - 05/22/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
     </row>
     <row r="6" ht="25" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
@@ -821,23 +771,23 @@
           <t>7000 - INFORMATION TECHNOLOGY</t>
         </is>
       </c>
-      <c r="C13" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D13" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E13" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F13" s="2" t="e">
-        <v>#N/A</v>
+      <c r="C13" s="5" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>37.5</v>
       </c>
-      <c r="H13" s="5" t="e">
-        <v>#N/A</v>
+      <c r="H13" s="7" t="n">
+        <v>7.1</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
@@ -880,698 +830,9 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Week: 05/11/2026 - 05/15/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="n"/>
-      <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="n"/>
-      <c r="E18" s="8" t="n"/>
-      <c r="F18" s="8" t="n"/>
-      <c r="G18" s="8" t="n"/>
-      <c r="H18" s="8" t="n"/>
-      <c r="I18" s="9" t="n"/>
-    </row>
-    <row r="19" ht="25" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Department</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Productive Active Hrs</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>Productive Passive Hrs</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>Total Productive Hrs</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>Active Days</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>GOAL</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>Productive Hrs/Day</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Angie Carolina Guaman</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>7000 - INFORMATION TECHNOLOGY</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="D20" s="6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H20" s="7" t="n">
-        <v>8.574999999999999</v>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Daniel Uribe</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>7000 - INFORMATION TECHNOLOGY</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="D21" s="6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H21" s="6" t="n">
-        <v>6.52</v>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>David Velasquez</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>7000 - INFORMATION TECHNOLOGY</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="D22" s="6" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="E22" s="5" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H22" s="6" t="n">
-        <v>6.36</v>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Juan David Londono</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>7000 - INFORMATION TECHNOLOGY</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="E23" s="5" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H23" s="7" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Juan Jose Gonzalez</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>7000 - INFORMATION TECHNOLOGY</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="D24" s="6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="E24" s="5" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H24" s="7" t="n">
-        <v>8.225</v>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>PTO 05/06</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Luis Aznar</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>7000 - INFORMATION TECHNOLOGY</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="D25" s="6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="E25" s="5" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H25" s="6" t="n">
-        <v>6.58</v>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Paulina Parra</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>7000 - INFORMATION TECHNOLOGY</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D26" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E26" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F26" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H26" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>Sick leave</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Sheyla Salvatierra</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>7000 - INFORMATION TECHNOLOGY</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="D27" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E27" s="5" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H27" s="7" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>PTO 05/07 y 05/08</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>Week: 05/18/2026 - 05/22/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n"/>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="2" t="n"/>
-      <c r="E31" s="2" t="n"/>
-      <c r="F31" s="2" t="n"/>
-      <c r="G31" s="2" t="n"/>
-      <c r="H31" s="2" t="n"/>
-      <c r="I31" s="2" t="n"/>
-    </row>
-    <row r="32" ht="25" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>Department</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>Productive Active Hrs</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>Productive Passive Hrs</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>Total Productive Hrs</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>Active Days</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t>GOAL</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>Productive Hrs/Day</t>
-        </is>
-      </c>
-      <c r="I32" s="4" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>Angie Carolina Guaman</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>7000 - INFORMATION TECHNOLOGY</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="D33" s="6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="E33" s="5" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="F33" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H33" s="7" t="n">
-        <v>8.574999999999999</v>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>Daniel Uribe</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>7000 - INFORMATION TECHNOLOGY</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="D34" s="6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="E34" s="5" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="F34" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H34" s="6" t="n">
-        <v>6.52</v>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>David Velasquez</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>7000 - INFORMATION TECHNOLOGY</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="D35" s="6" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="E35" s="5" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="F35" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G35" s="2" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H35" s="6" t="n">
-        <v>6.36</v>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Juan David Londono</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>7000 - INFORMATION TECHNOLOGY</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="D36" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="E36" s="5" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="F36" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H36" s="7" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>Juan Jose Gonzalez</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>7000 - INFORMATION TECHNOLOGY</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="D37" s="6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="E37" s="5" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="F37" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G37" s="2" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H37" s="7" t="n">
-        <v>8.225</v>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>PTO 05/06</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>Luis Aznar</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>7000 - INFORMATION TECHNOLOGY</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="D38" s="6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="E38" s="5" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="F38" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G38" s="2" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H38" s="6" t="n">
-        <v>6.58</v>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>Paulina Parra</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>7000 - INFORMATION TECHNOLOGY</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="D39" s="6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="E39" s="5" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="F39" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G39" s="2" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H39" s="7" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>Sick leave</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>Sheyla Salvatierra</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>7000 - INFORMATION TECHNOLOGY</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="D40" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E40" s="5" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="F40" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H40" s="7" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>PTO 05/07 y 05/08</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="1">
     <mergeCell ref="A5:I5"/>
-    <mergeCell ref="A18:I18"/>
-    <mergeCell ref="A31:I31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
